--- a/cross_border.xlsx
+++ b/cross_border.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2040BCB9-BCD2-4DAB-A96F-26ADAE94665C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E21FCA-7EAF-4AAF-8F15-15E29BA2F249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>company</t>
   </si>
@@ -55,6 +55,123 @@
   </si>
   <si>
     <t>judy@freightmark.co.th</t>
+  </si>
+  <si>
+    <t>PK Interfreight</t>
+  </si>
+  <si>
+    <t>K. Wanisa</t>
+  </si>
+  <si>
+    <t>K. Vee-onn (Sales Mgr.)</t>
+  </si>
+  <si>
+    <t>veeonn@pkinterfreight.co.th</t>
+  </si>
+  <si>
+    <t>Sirisomboonsub Transport lp.</t>
+  </si>
+  <si>
+    <t>K.Jay</t>
+  </si>
+  <si>
+    <t>061-021-7565</t>
+  </si>
+  <si>
+    <t>Laos</t>
+  </si>
+  <si>
+    <t>091-232-3345</t>
+  </si>
+  <si>
+    <t>wanisa@pkinterfreight.co.th</t>
+  </si>
+  <si>
+    <t>srb_t@hotmail.com</t>
+  </si>
+  <si>
+    <t>091-576-2056, 083-664-2296</t>
+  </si>
+  <si>
+    <t>Truking from BKK-Maesod</t>
+  </si>
+  <si>
+    <t>TNTT Logistics</t>
+  </si>
+  <si>
+    <t>K.Voo</t>
+  </si>
+  <si>
+    <t>Sky International Transport</t>
+  </si>
+  <si>
+    <t>K. Aeh</t>
+  </si>
+  <si>
+    <t>Malaysia, Singapore</t>
+  </si>
+  <si>
+    <t>Cambodia, Laos</t>
+  </si>
+  <si>
+    <t>sales@skyinter.co.th</t>
+  </si>
+  <si>
+    <t>Pongsiri Logistics</t>
+  </si>
+  <si>
+    <t>K. Tony</t>
+  </si>
+  <si>
+    <t>City Zone Express</t>
+  </si>
+  <si>
+    <t>K. Champ(Sales)</t>
+  </si>
+  <si>
+    <t>K. Nui(CS)</t>
+  </si>
+  <si>
+    <t>Overland Total Logistics (Thailand) Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>K. พลอย</t>
+  </si>
+  <si>
+    <t>Malaysia, Singapore, Cambodia</t>
+  </si>
+  <si>
+    <t>081-608-2588</t>
+  </si>
+  <si>
+    <t>089-146-5227</t>
+  </si>
+  <si>
+    <t>095-738-6460</t>
+  </si>
+  <si>
+    <t>thanyaboon@pongsiri.co.th</t>
+  </si>
+  <si>
+    <t>081-005-9090</t>
+  </si>
+  <si>
+    <t>champ@czoneasia.com</t>
+  </si>
+  <si>
+    <t>Malaysia, Singapore, China, Vietnam</t>
+  </si>
+  <si>
+    <t>pornpimon@czoneasia.com</t>
+  </si>
+  <si>
+    <t>090-978-8716</t>
+  </si>
+  <si>
+    <t>ploypailin@otlgp.com</t>
+  </si>
+  <si>
+    <t>065-919-5244</t>
   </si>
 </sst>
 </file>
@@ -393,14 +510,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -437,9 +555,164 @@
         <v>8</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{282D000F-94BA-46BA-BDA0-B6F0D8C99C28}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{C9AD910E-139C-4DB6-B8F3-53AC6C73D122}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{D46E20D5-FE7F-4FCC-B03E-B2F8FFEB62F6}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{90582030-6880-4BAE-A622-EBED5A58928D}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{8658C7D8-7772-4DBC-A1ED-F1B0D508006E}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{62F55D8A-BF26-4570-99AC-7EF2E5116DF8}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{B7743E8D-C8A6-4670-AB1B-AFC8989CAC72}"/>
+    <hyperlink ref="C10" r:id="rId8" xr:uid="{D1E724C1-A479-43A3-9D64-8036BA2F122E}"/>
+    <hyperlink ref="C11" r:id="rId9" xr:uid="{9547BEF4-CE1F-4F44-843D-1774A8B10427}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cross_border.xlsx
+++ b/cross_border.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E21FCA-7EAF-4AAF-8F15-15E29BA2F249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACAD768B-A70C-4C04-B53F-666AAC84BE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>company</t>
   </si>
@@ -667,6 +667,9 @@
       <c r="D9" t="s">
         <v>42</v>
       </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
